--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487909_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487909_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3576</v>
+        <v>2.7592</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4913</v>
+        <v>2.1572</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8662</v>
+        <v>0.602</v>
       </c>
       <c r="G2" t="n">
         <v>0.2155</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6196</v>
+        <v>2.0213</v>
       </c>
       <c r="T2" t="n">
-        <v>4.0996</v>
+        <v>1.7655</v>
       </c>
       <c r="U2" t="n">
-        <v>0.52</v>
+        <v>0.2558</v>
       </c>
       <c r="V2" t="n">
         <v>0.1061</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0459</v>
+        <v>1.208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9466</v>
+        <v>1.2262</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0993</v>
+        <v>-0.0182</v>
       </c>
       <c r="G3" t="n">
         <v>0.1025</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5865</v>
+        <v>0.7486</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2948</v>
+        <v>0.5744</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2917</v>
+        <v>0.1743</v>
       </c>
       <c r="V3" t="n">
         <v>1.3975</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6075</v>
+        <v>1.1507</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4814</v>
+        <v>-0.008</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8739</v>
+        <v>1.1587</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4347</v>
+        <v>-0.2242</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9898</v>
+        <v>1.2968</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4449</v>
+        <v>-1.521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1658</v>
+        <v>0.4129</v>
       </c>
       <c r="K4" t="n">
-        <v>0.223</v>
+        <v>1.938</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0572</v>
+        <v>-1.5251</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6005</v>
+        <v>-0.6371</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2127</v>
+        <v>-0.6412</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3878</v>
+        <v>0.0041</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.496</v>
+        <v>0.8131</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3073</v>
+        <v>0.9735</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1886</v>
+        <v>-0.1604</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2112</v>
+        <v>0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>5.13</v>
+        <v>-0.3538</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9188</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1648</v>
+        <v>0.4928</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1834</v>
+        <v>0.2033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3482</v>
+        <v>0.2894</v>
       </c>
       <c r="G5" t="n">
         <v>0.07340000000000001</v>
@@ -844,13 +844,13 @@
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1168</v>
+        <v>0.2112</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.261</v>
+        <v>0.1257</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1442</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5952</v>
+        <v>-0.0745</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9885</v>
+        <v>3.0342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3933</v>
+        <v>-3.1088</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1005</v>
+        <v>-1.4347</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2345</v>
+        <v>-0.9898</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.134</v>
+        <v>-0.4449</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4913</v>
+        <v>0.1658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8591</v>
+        <v>0.223</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3504</v>
+        <v>-0.0572</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5918</v>
+        <v>-1.6005</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3755</v>
+        <v>-1.2127</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2164</v>
+        <v>-0.3878</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4162</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4719</v>
+        <v>0.8139</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5434</v>
+        <v>0.8601</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9284</v>
+        <v>-0.0463</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7513</v>
+        <v>2.2112</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7513</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8784</v>
+        <v>-1.1133</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5967</v>
+        <v>-1.0956</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7183</v>
+        <v>-0.0177</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2242</v>
+        <v>0.1005</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2968</v>
+        <v>1.2345</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.521</v>
+        <v>-1.134</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4129</v>
+        <v>-0.4913</v>
       </c>
       <c r="K7" t="n">
-        <v>1.938</v>
+        <v>0.8591</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5251</v>
+        <v>-1.3504</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6371</v>
+        <v>0.5918</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6412</v>
+        <v>0.3755</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0041</v>
+        <v>0.2164</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2161</v>
+        <v>0.9537</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6153</v>
+        <v>0.4363</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6008</v>
+        <v>0.5174</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3538</v>
+        <v>-1.7513</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7076</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6717</v>
+        <v>-2.5316</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7287</v>
+        <v>-2.4255</v>
       </c>
       <c r="F8" t="n">
-        <v>0.057</v>
+        <v>-0.1061</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1614</v>
+        <v>-1.0333</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4031</v>
+        <v>-2.0939</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2417</v>
+        <v>1.0605</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7286</v>
+        <v>-0.7882</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3948</v>
+        <v>-2.4162</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6662</v>
+        <v>1.6279</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4328</v>
+        <v>-0.2451</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0083</v>
+        <v>0.3223</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4245</v>
+        <v>-0.5674</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0406</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0517</v>
+        <v>1.4591</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7887</v>
+        <v>1.4845</v>
       </c>
       <c r="U8" t="n">
-        <v>0.263</v>
+        <v>-0.0254</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5213</v>
+        <v>-0.4599</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8137</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0754</v>
+        <v>-3.1906</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7051</v>
+        <v>-3.3064</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3703</v>
+        <v>0.1157</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0333</v>
+        <v>-1.1614</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0939</v>
+        <v>-1.4031</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0605</v>
+        <v>0.2417</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7882</v>
+        <v>-0.7286</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.4162</v>
+        <v>-1.3948</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6279</v>
+        <v>0.6662</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2451</v>
+        <v>-0.4328</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3223</v>
+        <v>-0.0083</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5674</v>
+        <v>-0.4245</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4974</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9153</v>
+        <v>0.5327</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2049</v>
+        <v>0.211</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2896</v>
+        <v>0.3217</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4599</v>
+        <v>-1.5213</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4599</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8321</v>
+        <v>-4.7857</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8252</v>
+        <v>-1.8375</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0069</v>
+        <v>-2.9482</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3404</v>
@@ -1234,13 +1234,13 @@
         <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7405</v>
+        <v>0.306</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3915</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.349</v>
+        <v>-0.2903</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3351</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.2578</v>
+        <v>-7.0711</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7143</v>
+        <v>-2.7919</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5434</v>
+        <v>-4.2792</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7074</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0478</v>
+        <v>0.139</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5748</v>
+        <v>0.3477</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.473</v>
+        <v>-0.2087</v>
       </c>
       <c r="V11" t="n">
         <v>-3.5026</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.1348</v>
+        <v>-13.1561</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8226</v>
+        <v>-4.843999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.312200000000001</v>
+        <v>-8.3124</v>
       </c>
       <c r="G12" t="n">
         <v>-9.4095</v>
@@ -1390,13 +1390,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>7.019799999999998</v>
+        <v>7.9986</v>
       </c>
       <c r="T12" t="n">
-        <v>6.3961</v>
+        <v>7.375</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6236</v>
       </c>
       <c r="V12" t="n">
         <v>-5.501600000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8957</v>
+        <v>4.8133</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3385</v>
+        <v>1.7741</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5572</v>
+        <v>3.0392</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8174</v>
+        <v>3.3634</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0826</v>
+        <v>1.1917</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7348</v>
+        <v>2.1717</v>
       </c>
       <c r="J13" t="n">
-        <v>1.34</v>
+        <v>2.1308</v>
       </c>
       <c r="K13" t="n">
-        <v>1.144</v>
+        <v>0.6775</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1959</v>
+        <v>1.4532</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4774</v>
+        <v>1.2327</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0614</v>
+        <v>0.5142</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5389</v>
+        <v>0.7185</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2893</v>
+        <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2844</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.034</v>
+        <v>-0.109</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7496</v>
+        <v>-0.6908</v>
       </c>
       <c r="V13" t="n">
-        <v>3.6264</v>
+        <v>-0.2477</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0863</v>
+        <v>-0.2477</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8679</v>
+        <v>4.383</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8741</v>
+        <v>2.4813</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0062</v>
+        <v>1.9017</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2262</v>
+        <v>1.8174</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.196</v>
+        <v>1.0826</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0302</v>
+        <v>0.7348</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5987</v>
+        <v>1.34</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4901</v>
+        <v>1.144</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1086</v>
+        <v>0.1959</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8249</v>
+        <v>0.4774</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6861</v>
+        <v>-0.0614</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1388</v>
+        <v>0.5389</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4053</v>
+        <v>-0.2284</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2297</v>
+        <v>0.1767</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1756</v>
+        <v>-0.4051</v>
       </c>
       <c r="V14" t="n">
-        <v>3.2726</v>
+        <v>3.6264</v>
       </c>
       <c r="W14" t="n">
         <v>4.0863</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8137</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2593</v>
+        <v>3.8369</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9167999999999999</v>
+        <v>3.9097</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3425</v>
+        <v>-0.0728</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3634</v>
+        <v>-0.2262</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1917</v>
+        <v>-0.196</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1717</v>
+        <v>-0.0302</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1308</v>
+        <v>0.5987</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6775</v>
+        <v>0.4901</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4532</v>
+        <v>0.1086</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2327</v>
+        <v>-0.8249</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5142</v>
+        <v>-0.6861</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7185</v>
+        <v>-0.1388</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.3539</v>
+        <v>0.3743</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9663</v>
+        <v>0.2653</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3876</v>
+        <v>0.109</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2477</v>
+        <v>3.2726</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2477</v>
+        <v>4.0863</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.633</v>
+        <v>2.0719</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1312</v>
+        <v>2.4527</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4983</v>
+        <v>-0.3808</v>
       </c>
       <c r="G16" t="n">
         <v>2.9427</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9747</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3223</v>
+        <v>-0.2048</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2306</v>
+        <v>1.2076</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2072</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0234</v>
+        <v>1.1076</v>
       </c>
       <c r="G17" t="n">
         <v>0.8131</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0393</v>
+        <v>-1.0623</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0743</v>
+        <v>-0.0328</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1136</v>
+        <v>-1.0294</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9165</v>
+        <v>1.0951</v>
       </c>
       <c r="E18" t="n">
-        <v>0.873</v>
+        <v>0.7658</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0435</v>
+        <v>0.3293</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5649</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.7968</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1757</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.6211</v>
       </c>
       <c r="V18" t="n">
         <v>0.5838</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7067</v>
+        <v>0.7422</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4333</v>
+        <v>-0.9605</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7266</v>
+        <v>1.7026</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7591</v>
+        <v>1.127</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0424</v>
+        <v>-0.0617</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2833</v>
+        <v>1.1887</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4489</v>
+        <v>1.1028</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.2406</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2139</v>
+        <v>0.8621</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3102</v>
+        <v>0.0242</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3796</v>
+        <v>-0.3023</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0694</v>
+        <v>0.3266</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1182</v>
+        <v>-0.9062</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9844000000000001</v>
+        <v>-0.109</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1338</v>
+        <v>-0.7972</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2112</v>
+        <v>0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2112</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.162</v>
+        <v>-0.1941</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8177</v>
+        <v>0.6832</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6557</v>
+        <v>-0.8773</v>
       </c>
       <c r="G20" t="n">
-        <v>1.127</v>
+        <v>0.7591</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0617</v>
+        <v>1.0424</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1887</v>
+        <v>-0.2833</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1028</v>
+        <v>0.4489</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2406</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8621</v>
+        <v>-0.2139</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0242</v>
+        <v>0.3102</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3023</v>
+        <v>0.3796</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3266</v>
+        <v>-0.0694</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8104</v>
+        <v>0.2174</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9663</v>
+        <v>0.2343</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8441</v>
+        <v>-0.0169</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9376</v>
+        <v>-2.2112</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-2.2112</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1102</v>
+        <v>-0.2514</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4775</v>
+        <v>-0.9417</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3673</v>
+        <v>0.6902</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0667</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3348</v>
+        <v>-0.4761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9786</v>
+        <v>-0.4429</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3562</v>
+        <v>-0.0332</v>
       </c>
       <c r="V21" t="n">
         <v>0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1028</v>
+        <v>-1.4266</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1668</v>
+        <v>-1.9525</v>
       </c>
       <c r="F22" t="n">
-        <v>0.064</v>
+        <v>0.5259</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5553</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3394</v>
+        <v>-0.6632</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0256</v>
+        <v>-0.5637</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.1347</v>
+        <v>16.2779</v>
       </c>
       <c r="E23" t="n">
-        <v>8.312099999999999</v>
+        <v>8.312099999999997</v>
       </c>
       <c r="F23" t="n">
-        <v>5.8225</v>
+        <v>7.9656</v>
       </c>
       <c r="G23" t="n">
         <v>9.409599999999998</v>
@@ -2218,7 +2218,7 @@
         <v>2.633300000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>6.7764</v>
+        <v>6.776400000000001</v>
       </c>
       <c r="J23" t="n">
         <v>7.227499999999999</v>
@@ -2248,13 +2248,13 @@
         <v>15.6089</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.019899999999998</v>
+        <v>-4.877</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6234999999999999</v>
+        <v>-0.6236</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.3964</v>
+        <v>-4.2532</v>
       </c>
       <c r="V23" t="n">
         <v>5.501600000000001</v>
